--- a/r_test/nbclust_analysis/AN_TJ_1_pc_selection_most_frequent_number.xlsx
+++ b/r_test/nbclust_analysis/AN_TJ_1_pc_selection_most_frequent_number.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t xml:space="preserve">index</t>
   </si>
@@ -21,45 +21,6 @@
   </si>
   <si>
     <t xml:space="preserve">ratkowsky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ptbiserial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sdbw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">db</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sdindex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dunn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ball</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tracew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">friedman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rubin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pseudot2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">beale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trcovw</t>
   </si>
 </sst>
 </file>
@@ -401,110 +362,6 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="n">
         <v>3</v>
       </c>
     </row>
